--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/137.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/137.xlsx
@@ -426,13 +426,13 @@
         <v>-17.42805988044556</v>
       </c>
       <c r="E2">
-        <v>-8.623615885780334</v>
+        <v>-7.915412364194773</v>
       </c>
       <c r="F2">
-        <v>-4.827575436263119</v>
+        <v>-5.279878120437497</v>
       </c>
       <c r="G2">
-        <v>-8.428100543093256</v>
+        <v>-6.621913244504447</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.29520296119705</v>
       </c>
       <c r="E3">
-        <v>-9.284197974701231</v>
+        <v>-8.686769984291303</v>
       </c>
       <c r="F3">
-        <v>-4.668306064094262</v>
+        <v>-5.41478769239223</v>
       </c>
       <c r="G3">
-        <v>-8.5768930123558</v>
+        <v>-6.092411348771257</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.06313960434991</v>
       </c>
       <c r="E4">
-        <v>-10.01713602131669</v>
+        <v>-8.858752370154608</v>
       </c>
       <c r="F4">
-        <v>-4.748265884384289</v>
+        <v>-5.478031886861167</v>
       </c>
       <c r="G4">
-        <v>-7.596203486166418</v>
+        <v>-6.726589383910663</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.73638538107265</v>
       </c>
       <c r="E5">
-        <v>-10.85045675126017</v>
+        <v>-9.776963873845881</v>
       </c>
       <c r="F5">
-        <v>-4.668878465969596</v>
+        <v>-5.319768152719307</v>
       </c>
       <c r="G5">
-        <v>-8.183328737556163</v>
+        <v>-6.354983957673012</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.31172731393043</v>
       </c>
       <c r="E6">
-        <v>-10.87875065686009</v>
+        <v>-10.80054391074763</v>
       </c>
       <c r="F6">
-        <v>-5.139341448715547</v>
+        <v>-5.125953374751502</v>
       </c>
       <c r="G6">
-        <v>-7.776850024607829</v>
+        <v>-5.810455495737068</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.79824935590662</v>
       </c>
       <c r="E7">
-        <v>-11.75204875534329</v>
+        <v>-11.04493206751957</v>
       </c>
       <c r="F7">
-        <v>-4.879606849567763</v>
+        <v>-5.252708497993076</v>
       </c>
       <c r="G7">
-        <v>-8.009389364377316</v>
+        <v>-6.183421556191361</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.19856946760016</v>
       </c>
       <c r="E8">
-        <v>-11.46986595450333</v>
+        <v>-12.70760205570181</v>
       </c>
       <c r="F8">
-        <v>-4.468424323268352</v>
+        <v>-5.125199560414954</v>
       </c>
       <c r="G8">
-        <v>-7.603764772178113</v>
+        <v>-5.695331274608913</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.50635498277137</v>
       </c>
       <c r="E9">
-        <v>-12.55103459536062</v>
+        <v>-13.39591651944568</v>
       </c>
       <c r="F9">
-        <v>-4.638899021294879</v>
+        <v>-4.8784048884663</v>
       </c>
       <c r="G9">
-        <v>-7.032904231022808</v>
+        <v>-5.383782454999181</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.71480209810518</v>
       </c>
       <c r="E10">
-        <v>-14.96373309106326</v>
+        <v>-15.03654642463259</v>
       </c>
       <c r="F10">
-        <v>-4.521565748892746</v>
+        <v>-5.094695759174265</v>
       </c>
       <c r="G10">
-        <v>-6.965057910740985</v>
+        <v>-5.266049523986079</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.83695202144361</v>
       </c>
       <c r="E11">
-        <v>-15.86029848899787</v>
+        <v>-15.25785747786145</v>
       </c>
       <c r="F11">
-        <v>-4.44568977989852</v>
+        <v>-4.69812894732985</v>
       </c>
       <c r="G11">
-        <v>-6.624379600931205</v>
+        <v>-4.876729368567788</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.890684877792</v>
       </c>
       <c r="E12">
-        <v>-16.67530154158033</v>
+        <v>-15.42001760360212</v>
       </c>
       <c r="F12">
-        <v>-4.500998214648637</v>
+        <v>-4.693902616840766</v>
       </c>
       <c r="G12">
-        <v>-5.930926247911147</v>
+        <v>-4.99727295274373</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.89942448072779</v>
       </c>
       <c r="E13">
-        <v>-16.26887099939191</v>
+        <v>-17.01207962505676</v>
       </c>
       <c r="F13">
-        <v>-4.704478383472308</v>
+        <v>-5.002914307678886</v>
       </c>
       <c r="G13">
-        <v>-6.106772495320615</v>
+        <v>-4.255611435580806</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.919833729899988</v>
       </c>
       <c r="E14">
-        <v>-18.07462265232051</v>
+        <v>-17.24013810455705</v>
       </c>
       <c r="F14">
-        <v>-4.514612432913647</v>
+        <v>-4.671974074953858</v>
       </c>
       <c r="G14">
-        <v>-6.238952647067095</v>
+        <v>-3.98186904602955</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.008699860931394</v>
       </c>
       <c r="E15">
-        <v>-19.57938928032929</v>
+        <v>-18.8084075235754</v>
       </c>
       <c r="F15">
-        <v>-4.171416504464201</v>
+        <v>-4.447981044134663</v>
       </c>
       <c r="G15">
-        <v>-4.778280365320941</v>
+        <v>-3.450834367711677</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.212367056968018</v>
       </c>
       <c r="E16">
-        <v>-18.57467033766949</v>
+        <v>-20.27614934809747</v>
       </c>
       <c r="F16">
-        <v>-3.882630232132834</v>
+        <v>-4.072429084931868</v>
       </c>
       <c r="G16">
-        <v>-4.998292600769825</v>
+        <v>-3.074991443183758</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.57261193842929</v>
       </c>
       <c r="E17">
-        <v>-20.09930790962393</v>
+        <v>-20.38774906154249</v>
       </c>
       <c r="F17">
-        <v>-3.844588287526669</v>
+        <v>-4.058659961962535</v>
       </c>
       <c r="G17">
-        <v>-4.177072053207136</v>
+        <v>-3.134495188706619</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.11857322358514</v>
       </c>
       <c r="E18">
-        <v>-20.11619458919854</v>
+        <v>-21.52768370959732</v>
       </c>
       <c r="F18">
-        <v>-3.762549265055615</v>
+        <v>-3.69787945028646</v>
       </c>
       <c r="G18">
-        <v>-4.928238146613308</v>
+        <v>-3.217361454100116</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.855158622781239</v>
       </c>
       <c r="E19">
-        <v>-22.14145949117494</v>
+        <v>-21.53802221575684</v>
       </c>
       <c r="F19">
-        <v>-3.731310701928643</v>
+        <v>-3.582928562534779</v>
       </c>
       <c r="G19">
-        <v>-5.603079612611582</v>
+        <v>-3.937640157624887</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.771492466455604</v>
       </c>
       <c r="E20">
-        <v>-21.29320838242817</v>
+        <v>-23.10241978949862</v>
       </c>
       <c r="F20">
-        <v>-3.135338460514927</v>
+        <v>-3.040074552458178</v>
       </c>
       <c r="G20">
-        <v>-4.56792830175565</v>
+        <v>-4.114972839981488</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.864522885227542</v>
       </c>
       <c r="E21">
-        <v>-22.31888510279547</v>
+        <v>-23.52784728014921</v>
       </c>
       <c r="F21">
-        <v>-2.666341688071931</v>
+        <v>-2.9480271950265</v>
       </c>
       <c r="G21">
-        <v>-4.599083845825731</v>
+        <v>-3.882506332213865</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.114102722535153</v>
       </c>
       <c r="E22">
-        <v>-23.54149610080833</v>
+        <v>-23.44413843811743</v>
       </c>
       <c r="F22">
-        <v>-2.221922576469996</v>
+        <v>-2.622374431433542</v>
       </c>
       <c r="G22">
-        <v>-4.4945666126054</v>
+        <v>-4.402715526618321</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.482802855630457</v>
       </c>
       <c r="E23">
-        <v>-23.47623626188379</v>
+        <v>-23.46801255308586</v>
       </c>
       <c r="F23">
-        <v>-2.281241966184469</v>
+        <v>-2.390057964951018</v>
       </c>
       <c r="G23">
-        <v>-5.168858528044155</v>
+        <v>-4.366915287156643</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.940192608753225</v>
       </c>
       <c r="E24">
-        <v>-24.22837050981776</v>
+        <v>-24.63196622727738</v>
       </c>
       <c r="F24">
-        <v>-1.750725660205165</v>
+        <v>-2.404715097776152</v>
       </c>
       <c r="G24">
-        <v>-6.272127623916132</v>
+        <v>-4.361538961200866</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.44915145647678</v>
       </c>
       <c r="E25">
-        <v>-23.30233833151524</v>
+        <v>-24.11590585783727</v>
       </c>
       <c r="F25">
-        <v>-2.058329954825928</v>
+        <v>-2.068436037140082</v>
       </c>
       <c r="G25">
-        <v>-5.78101812480187</v>
+        <v>-4.941728619685838</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.968235650848046</v>
       </c>
       <c r="E26">
-        <v>-24.3095117070872</v>
+        <v>-24.51614144758319</v>
       </c>
       <c r="F26">
-        <v>-1.815352399869374</v>
+        <v>-1.895549961604005</v>
       </c>
       <c r="G26">
-        <v>-6.190360459641673</v>
+        <v>-5.421539226874568</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.464081231460478</v>
       </c>
       <c r="E27">
-        <v>-24.24359523943155</v>
+        <v>-24.6313322409163</v>
       </c>
       <c r="F27">
-        <v>-2.012892346047569</v>
+        <v>-1.672723272087952</v>
       </c>
       <c r="G27">
-        <v>-6.421131968093189</v>
+        <v>-5.782709813572437</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.916747273673566</v>
       </c>
       <c r="E28">
-        <v>-23.83136825051332</v>
+        <v>-24.06291818347352</v>
       </c>
       <c r="F28">
-        <v>-1.65173741230543</v>
+        <v>-1.534605433182177</v>
       </c>
       <c r="G28">
-        <v>-6.003006755937699</v>
+        <v>-5.670578325611783</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.30980688393703</v>
       </c>
       <c r="E29">
-        <v>-23.51792539359841</v>
+        <v>-24.13005733911124</v>
       </c>
       <c r="F29">
-        <v>-1.743440168897543</v>
+        <v>-2.013416702613541</v>
       </c>
       <c r="G29">
-        <v>-6.898899968684189</v>
+        <v>-5.848791613081829</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.63120150863376</v>
       </c>
       <c r="E30">
-        <v>-23.58520040345636</v>
+        <v>-23.31065713826733</v>
       </c>
       <c r="F30">
-        <v>-1.496473196529107</v>
+        <v>-1.613127207660945</v>
       </c>
       <c r="G30">
-        <v>-6.237625118305848</v>
+        <v>-5.878705702574684</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.89278962440052</v>
       </c>
       <c r="E31">
-        <v>-22.61315892923591</v>
+        <v>-23.35541204688514</v>
       </c>
       <c r="F31">
-        <v>-1.624543767206327</v>
+        <v>-1.636227889422814</v>
       </c>
       <c r="G31">
-        <v>-7.128608792017599</v>
+        <v>-6.000560262784178</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.10746660497624</v>
       </c>
       <c r="E32">
-        <v>-23.0859950142728</v>
+        <v>-23.05513346391053</v>
       </c>
       <c r="F32">
-        <v>-1.291049677778469</v>
+        <v>-1.349340235178665</v>
       </c>
       <c r="G32">
-        <v>-6.141516670755266</v>
+        <v>-5.812375612149846</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.28802435195466</v>
       </c>
       <c r="E33">
-        <v>-22.98149141959779</v>
+        <v>-22.56878441243474</v>
       </c>
       <c r="F33">
-        <v>-1.735894570225442</v>
+        <v>-1.482402547825155</v>
       </c>
       <c r="G33">
-        <v>-5.993379689509498</v>
+        <v>-5.027829288071203</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.45892982053331</v>
       </c>
       <c r="E34">
-        <v>-22.6045955848874</v>
+        <v>-22.29751976242727</v>
       </c>
       <c r="F34">
-        <v>-1.49285820118329</v>
+        <v>-1.398343137258672</v>
       </c>
       <c r="G34">
-        <v>-6.38342485440089</v>
+        <v>-5.208621490516342</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.64332379839755</v>
       </c>
       <c r="E35">
-        <v>-22.46791265391389</v>
+        <v>-21.78934799470853</v>
       </c>
       <c r="F35">
-        <v>-1.187055605663616</v>
+        <v>-1.126310595648925</v>
       </c>
       <c r="G35">
-        <v>-6.532660936765696</v>
+        <v>-5.566958250232594</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.85411946014926</v>
       </c>
       <c r="E36">
-        <v>-21.10161317563764</v>
+        <v>-21.62967400119808</v>
       </c>
       <c r="F36">
-        <v>-1.239213759180887</v>
+        <v>-1.300976004366215</v>
       </c>
       <c r="G36">
-        <v>-4.849132660952423</v>
+        <v>-5.230391637982589</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.09601119521725</v>
       </c>
       <c r="E37">
-        <v>-21.30610547640201</v>
+        <v>-21.45968867237215</v>
       </c>
       <c r="F37">
-        <v>-1.283070014587301</v>
+        <v>-1.488032961061983</v>
       </c>
       <c r="G37">
-        <v>-6.150451833165759</v>
+        <v>-4.803807981974261</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.37284992703849</v>
       </c>
       <c r="E38">
-        <v>-19.70513141810027</v>
+        <v>-19.86987277402531</v>
       </c>
       <c r="F38">
-        <v>-1.212451693498643</v>
+        <v>-1.064349542286925</v>
       </c>
       <c r="G38">
-        <v>-5.52968481800594</v>
+        <v>-4.750809458436069</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.67217104903039</v>
       </c>
       <c r="E39">
-        <v>-19.78781229653232</v>
+        <v>-20.20269297121904</v>
       </c>
       <c r="F39">
-        <v>-1.228171621701569</v>
+        <v>-1.493443028569666</v>
       </c>
       <c r="G39">
-        <v>-5.83425169707335</v>
+        <v>-4.498191659970902</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.96717939774581</v>
       </c>
       <c r="E40">
-        <v>-18.28511065267103</v>
+        <v>-20.25026006219561</v>
       </c>
       <c r="F40">
-        <v>-1.157324671209739</v>
+        <v>-1.425207920498863</v>
       </c>
       <c r="G40">
-        <v>-4.903577892891277</v>
+        <v>-4.309712370783576</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.24511221552706</v>
       </c>
       <c r="E41">
-        <v>-19.03213225345034</v>
+        <v>-19.50890811087391</v>
       </c>
       <c r="F41">
-        <v>-1.348300634088151</v>
+        <v>-1.278267968753273</v>
       </c>
       <c r="G41">
-        <v>-4.957718554640518</v>
+        <v>-4.337693101681496</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.48687328090974</v>
       </c>
       <c r="E42">
-        <v>-18.65563945292664</v>
+        <v>-18.27229054275532</v>
       </c>
       <c r="F42">
-        <v>-1.567461797846816</v>
+        <v>-1.687764767387986</v>
       </c>
       <c r="G42">
-        <v>-5.090928286049712</v>
+        <v>-3.862252414604603</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.67106944133746</v>
       </c>
       <c r="E43">
-        <v>-18.40870629376238</v>
+        <v>-18.58230534484642</v>
       </c>
       <c r="F43">
-        <v>-1.519477787672252</v>
+        <v>-1.667016649050066</v>
       </c>
       <c r="G43">
-        <v>-4.485277221822205</v>
+        <v>-3.520326029126518</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.79061942208104</v>
       </c>
       <c r="E44">
-        <v>-18.15156595418483</v>
+        <v>-18.06749936270644</v>
       </c>
       <c r="F44">
-        <v>-1.546660663995118</v>
+        <v>-1.693800252284783</v>
       </c>
       <c r="G44">
-        <v>-5.048440744598706</v>
+        <v>-3.672922315213684</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.84735029457418</v>
       </c>
       <c r="E45">
-        <v>-17.3359832569294</v>
+        <v>-16.33788947174282</v>
       </c>
       <c r="F45">
-        <v>-1.966703408034872</v>
+        <v>-1.790070626735933</v>
       </c>
       <c r="G45">
-        <v>-5.032076717998088</v>
+        <v>-3.608287224104954</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.84275296976414</v>
       </c>
       <c r="E46">
-        <v>-17.49553498164164</v>
+        <v>-17.1251012793402</v>
       </c>
       <c r="F46">
-        <v>-1.983650148361344</v>
+        <v>-1.921399166408364</v>
       </c>
       <c r="G46">
-        <v>-4.036128887418204</v>
+        <v>-2.568653434588848</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.78022668483741</v>
       </c>
       <c r="E47">
-        <v>-17.07212719039847</v>
+        <v>-16.16514177377222</v>
       </c>
       <c r="F47">
-        <v>-1.779894961559944</v>
+        <v>-2.214874826606978</v>
       </c>
       <c r="G47">
-        <v>-4.542559591288215</v>
+        <v>-3.195439021539062</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.67875965349411</v>
       </c>
       <c r="E48">
-        <v>-14.91820834186415</v>
+        <v>-15.55371174173057</v>
       </c>
       <c r="F48">
-        <v>-2.042432755998802</v>
+        <v>-2.097033764986929</v>
       </c>
       <c r="G48">
-        <v>-4.583534213427774</v>
+        <v>-3.329761096249451</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.54998553208523</v>
       </c>
       <c r="E49">
-        <v>-14.57384959289888</v>
+        <v>-15.18315577063092</v>
       </c>
       <c r="F49">
-        <v>-1.94175878043437</v>
+        <v>-2.24720517797084</v>
       </c>
       <c r="G49">
-        <v>-4.114655027609717</v>
+        <v>-2.803824658062055</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.39604915355354</v>
       </c>
       <c r="E50">
-        <v>-13.72201193273803</v>
+        <v>-14.67344432174957</v>
       </c>
       <c r="F50">
-        <v>-2.02585878100359</v>
+        <v>-2.180706327976304</v>
       </c>
       <c r="G50">
-        <v>-4.47112795018736</v>
+        <v>-2.557136046657723</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.2339381347746</v>
       </c>
       <c r="E51">
-        <v>-13.71477090279976</v>
+        <v>-14.55323597921596</v>
       </c>
       <c r="F51">
-        <v>-1.936598879882332</v>
+        <v>-2.268954792498744</v>
       </c>
       <c r="G51">
-        <v>-4.496218574829497</v>
+        <v>-2.618808199508806</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.07229746635497</v>
       </c>
       <c r="E52">
-        <v>-14.14133051195227</v>
+        <v>-12.78541482457561</v>
       </c>
       <c r="F52">
-        <v>-2.099149415333679</v>
+        <v>-2.403002862354565</v>
       </c>
       <c r="G52">
-        <v>-4.43497017180744</v>
+        <v>-2.700744201605768</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.91023727035756</v>
       </c>
       <c r="E53">
-        <v>-13.10471299838244</v>
+        <v>-12.6906519774911</v>
       </c>
       <c r="F53">
-        <v>-2.117568164534926</v>
+        <v>-2.607626178194099</v>
       </c>
       <c r="G53">
-        <v>-3.785030629355564</v>
+        <v>-2.839376606608289</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.74987067839276</v>
       </c>
       <c r="E54">
-        <v>-12.26378443210607</v>
+        <v>-12.32376859881168</v>
       </c>
       <c r="F54">
-        <v>-2.408357429246262</v>
+        <v>-2.774137966565634</v>
       </c>
       <c r="G54">
-        <v>-4.234361043764224</v>
+        <v>-3.325301791408052</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.59628367257627</v>
       </c>
       <c r="E55">
-        <v>-10.82886045871759</v>
+        <v>-11.16872243299325</v>
       </c>
       <c r="F55">
-        <v>-2.000295362953197</v>
+        <v>-2.42062472211432</v>
       </c>
       <c r="G55">
-        <v>-5.503554682064473</v>
+        <v>-3.075646931200534</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.44654124122642</v>
       </c>
       <c r="E56">
-        <v>-11.09269388287847</v>
+        <v>-11.3820588434946</v>
       </c>
       <c r="F56">
-        <v>-2.369420019477671</v>
+        <v>-2.412337734616713</v>
       </c>
       <c r="G56">
-        <v>-5.486472267081833</v>
+        <v>-3.109666097162084</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.29101520963855</v>
       </c>
       <c r="E57">
-        <v>-11.04383164833571</v>
+        <v>-11.0164343805893</v>
       </c>
       <c r="F57">
-        <v>-2.427761107289437</v>
+        <v>-2.634712135530838</v>
       </c>
       <c r="G57">
-        <v>-5.804880537048936</v>
+        <v>-2.997279697194907</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.13409247485418</v>
       </c>
       <c r="E58">
-        <v>-11.07426299366725</v>
+        <v>-11.18328147692791</v>
       </c>
       <c r="F58">
-        <v>-2.052996925486704</v>
+        <v>-2.369815150728806</v>
       </c>
       <c r="G58">
-        <v>-5.763929088728151</v>
+        <v>-3.351865608815165</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.97111488451894</v>
       </c>
       <c r="E59">
-        <v>-10.49826827073563</v>
+        <v>-11.16427547151772</v>
       </c>
       <c r="F59">
-        <v>-1.815474169877585</v>
+        <v>-2.720246040074303</v>
       </c>
       <c r="G59">
-        <v>-5.87063790309548</v>
+        <v>-3.211687179045805</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.78993854550599</v>
       </c>
       <c r="E60">
-        <v>-8.743910269320088</v>
+        <v>-10.57983514456179</v>
       </c>
       <c r="F60">
-        <v>-2.339718906250295</v>
+        <v>-2.284043504740737</v>
       </c>
       <c r="G60">
-        <v>-5.495970222234003</v>
+        <v>-3.577171406581344</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.59074046618138</v>
       </c>
       <c r="E61">
-        <v>-9.397124531030506</v>
+        <v>-10.32047585272048</v>
       </c>
       <c r="F61">
-        <v>-2.499793451534674</v>
+        <v>-2.366980477476426</v>
       </c>
       <c r="G61">
-        <v>-5.192939436296815</v>
+        <v>-3.493394741164547</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.37099675867738</v>
       </c>
       <c r="E62">
-        <v>-8.83697946712573</v>
+        <v>-10.03493292416683</v>
       </c>
       <c r="F62">
-        <v>-2.196613467212263</v>
+        <v>-2.362668825144855</v>
       </c>
       <c r="G62">
-        <v>-5.802225479526441</v>
+        <v>-3.836006409569261</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.12404989070616</v>
       </c>
       <c r="E63">
-        <v>-9.632301771670852</v>
+        <v>-9.043912615380234</v>
       </c>
       <c r="F63">
-        <v>-2.423528978228535</v>
+        <v>-2.517071538822266</v>
       </c>
       <c r="G63">
-        <v>-6.039763743060226</v>
+        <v>-4.059415264741438</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.84812136505467</v>
       </c>
       <c r="E64">
-        <v>-9.108588281157783</v>
+        <v>-8.52932399999262</v>
       </c>
       <c r="F64">
-        <v>-2.54597327750594</v>
+        <v>-2.506881791400429</v>
       </c>
       <c r="G64">
-        <v>-5.702697238433792</v>
+        <v>-4.211965203191054</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.55119661750165</v>
       </c>
       <c r="E65">
-        <v>-8.786296786031883</v>
+        <v>-9.713932044133117</v>
       </c>
       <c r="F65">
-        <v>-2.471674520046645</v>
+        <v>-2.57696830061649</v>
       </c>
       <c r="G65">
-        <v>-5.476977622475204</v>
+        <v>-4.501075145135608</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.23765006835793</v>
       </c>
       <c r="E66">
-        <v>-7.380866763855357</v>
+        <v>-8.22443090200419</v>
       </c>
       <c r="F66">
-        <v>-2.595113688574813</v>
+        <v>-2.548742509733499</v>
       </c>
       <c r="G66">
-        <v>-5.752875177172525</v>
+        <v>-4.827173812390437</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.907389107110813</v>
       </c>
       <c r="E67">
-        <v>-7.168983993510468</v>
+        <v>-8.037192087209045</v>
       </c>
       <c r="F67">
-        <v>-2.132934379856857</v>
+        <v>-2.562878599462273</v>
       </c>
       <c r="G67">
-        <v>-6.002814744296421</v>
+        <v>-4.412230034498187</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.57510960211556</v>
       </c>
       <c r="E68">
-        <v>-7.832192597355815</v>
+        <v>-8.378036740344369</v>
       </c>
       <c r="F68">
-        <v>-2.516831312275454</v>
+        <v>-2.675697269519149</v>
       </c>
       <c r="G68">
-        <v>-5.599421459790688</v>
+        <v>-3.956728763204325</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.249060218105631</v>
       </c>
       <c r="E69">
-        <v>-6.741500575660394</v>
+        <v>-7.577434235106304</v>
       </c>
       <c r="F69">
-        <v>-2.3283876685474</v>
+        <v>-2.406964943642155</v>
       </c>
       <c r="G69">
-        <v>-6.297413570745086</v>
+        <v>-4.020460075380834</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.929989379256691</v>
       </c>
       <c r="E70">
-        <v>-7.439356534138427</v>
+        <v>-8.501627852961709</v>
       </c>
       <c r="F70">
-        <v>-2.229266053495814</v>
+        <v>-2.761394362440966</v>
       </c>
       <c r="G70">
-        <v>-6.949147428879247</v>
+        <v>-4.660193205935138</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.624940326562795</v>
       </c>
       <c r="E71">
-        <v>-8.247145727626664</v>
+        <v>-8.03659885711404</v>
       </c>
       <c r="F71">
-        <v>-2.934580306976856</v>
+        <v>-2.640679694300605</v>
       </c>
       <c r="G71">
-        <v>-5.810041677544659</v>
+        <v>-4.471905928389089</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.339155726410578</v>
       </c>
       <c r="E72">
-        <v>-8.182968193989961</v>
+        <v>-7.706717639551285</v>
       </c>
       <c r="F72">
-        <v>-2.463587997460516</v>
+        <v>-2.838904700320916</v>
       </c>
       <c r="G72">
-        <v>-6.031378131209252</v>
+        <v>-4.16065505787789</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.071019065581394</v>
       </c>
       <c r="E73">
-        <v>-8.359524338601013</v>
+        <v>-8.182601387595339</v>
       </c>
       <c r="F73">
-        <v>-3.024446573036963</v>
+        <v>-2.917616999302328</v>
       </c>
       <c r="G73">
-        <v>-6.323096783038752</v>
+        <v>-4.408773824955188</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.817141312058966</v>
       </c>
       <c r="E74">
-        <v>-9.031586109131355</v>
+        <v>-8.572385259331558</v>
       </c>
       <c r="F74">
-        <v>-2.850551546004277</v>
+        <v>-3.015638542442996</v>
       </c>
       <c r="G74">
-        <v>-6.316485623596827</v>
+        <v>-4.137520965649464</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.581298475090311</v>
       </c>
       <c r="E75">
-        <v>-8.147596283516048</v>
+        <v>-8.521584837913512</v>
       </c>
       <c r="F75">
-        <v>-3.013665371289528</v>
+        <v>-3.225101180649685</v>
       </c>
       <c r="G75">
-        <v>-5.053270830540503</v>
+        <v>-3.633308327290765</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.362455244053052</v>
       </c>
       <c r="E76">
-        <v>-8.669235732933604</v>
+        <v>-9.729713776049849</v>
       </c>
       <c r="F76">
-        <v>-3.133487059369671</v>
+        <v>-3.08074325009862</v>
       </c>
       <c r="G76">
-        <v>-4.858978223386216</v>
+        <v>-4.247159612819047</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.153921747293994</v>
       </c>
       <c r="E77">
-        <v>-8.45436869821766</v>
+        <v>-9.179694380026222</v>
       </c>
       <c r="F77">
-        <v>-3.184366213617019</v>
+        <v>-3.189449076000597</v>
       </c>
       <c r="G77">
-        <v>-5.521749440348307</v>
+        <v>-4.429004568745674</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.960356132790526</v>
       </c>
       <c r="E78">
-        <v>-10.04659374473658</v>
+        <v>-8.80282571615988</v>
       </c>
       <c r="F78">
-        <v>-3.816113158055437</v>
+        <v>-3.445089883443746</v>
       </c>
       <c r="G78">
-        <v>-4.971649330269771</v>
+        <v>-3.892053945549123</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.781575917845997</v>
       </c>
       <c r="E79">
-        <v>-10.82471237652656</v>
+        <v>-10.74906421822843</v>
       </c>
       <c r="F79">
-        <v>-3.868915781412086</v>
+        <v>-3.400025039996648</v>
       </c>
       <c r="G79">
-        <v>-4.958824276850635</v>
+        <v>-3.811293187118602</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.613454456631958</v>
       </c>
       <c r="E80">
-        <v>-9.926589183533316</v>
+        <v>-10.80993143736553</v>
       </c>
       <c r="F80">
-        <v>-4.08288059645299</v>
+        <v>-3.754386532668429</v>
       </c>
       <c r="G80">
-        <v>-4.801709096102363</v>
+        <v>-3.209886242272441</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.456468855230055</v>
       </c>
       <c r="E81">
-        <v>-11.84306655442346</v>
+        <v>-10.72698790744104</v>
       </c>
       <c r="F81">
-        <v>-3.624056175716371</v>
+        <v>-3.840954239730588</v>
       </c>
       <c r="G81">
-        <v>-4.582594018494621</v>
+        <v>-3.202060112617604</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.312779493776799</v>
       </c>
       <c r="E82">
-        <v>-11.81114534114339</v>
+        <v>-12.26589017251964</v>
       </c>
       <c r="F82">
-        <v>-3.785449481906007</v>
+        <v>-3.956312684244447</v>
       </c>
       <c r="G82">
-        <v>-4.312082721389694</v>
+        <v>-3.612266499843158</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.17992010158971</v>
       </c>
       <c r="E83">
-        <v>-13.54878421652261</v>
+        <v>-13.3861259586411</v>
       </c>
       <c r="F83">
-        <v>-4.235995198819047</v>
+        <v>-4.121837058671844</v>
       </c>
       <c r="G83">
-        <v>-4.916882975413608</v>
+        <v>-3.122765925860981</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.053141912722005</v>
       </c>
       <c r="E84">
-        <v>-13.0634767140686</v>
+        <v>-13.8445614963336</v>
       </c>
       <c r="F84">
-        <v>-4.3173234820585</v>
+        <v>-4.139956767240681</v>
       </c>
       <c r="G84">
-        <v>-4.627865728744155</v>
+        <v>-3.371656050048928</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.936289241599744</v>
       </c>
       <c r="E85">
-        <v>-15.11211307039859</v>
+        <v>-14.91600297502242</v>
       </c>
       <c r="F85">
-        <v>-4.381325632700998</v>
+        <v>-4.452752440374788</v>
       </c>
       <c r="G85">
-        <v>-4.61816914085963</v>
+        <v>-3.221605573481461</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.830219506324186</v>
       </c>
       <c r="E86">
-        <v>-17.18491336403351</v>
+        <v>-16.33561164931696</v>
       </c>
       <c r="F86">
-        <v>-4.680970973315663</v>
+        <v>-4.642599338483184</v>
       </c>
       <c r="G86">
-        <v>-4.393654563477336</v>
+        <v>-2.245259483039603</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.732608875550984</v>
       </c>
       <c r="E87">
-        <v>-17.99873448489997</v>
+        <v>-17.20271479535766</v>
       </c>
       <c r="F87">
-        <v>-5.082575087336503</v>
+        <v>-4.9457511583139</v>
       </c>
       <c r="G87">
-        <v>-4.014418329771664</v>
+        <v>-3.087439094411418</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.652249972063265</v>
       </c>
       <c r="E88">
-        <v>-18.64102153882988</v>
+        <v>-18.51322800233342</v>
       </c>
       <c r="F88">
-        <v>-5.2806186808956</v>
+        <v>-4.967214157720435</v>
       </c>
       <c r="G88">
-        <v>-4.384997486892142</v>
+        <v>-2.885694449248232</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.597821822075504</v>
       </c>
       <c r="E89">
-        <v>-19.32152891338453</v>
+        <v>-19.83634395247252</v>
       </c>
       <c r="F89">
-        <v>-5.15749263524569</v>
+        <v>-5.14566272036631</v>
       </c>
       <c r="G89">
-        <v>-3.710662534361376</v>
+        <v>-3.038297356426476</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.576519507011663</v>
       </c>
       <c r="E90">
-        <v>-22.437277527252</v>
+        <v>-21.49186348019665</v>
       </c>
       <c r="F90">
-        <v>-5.241340812124458</v>
+        <v>-5.337546573918191</v>
       </c>
       <c r="G90">
-        <v>-4.758105900804622</v>
+        <v>-2.828329316143741</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.599187212589122</v>
       </c>
       <c r="E91">
-        <v>-24.10914484614382</v>
+        <v>-23.12870758111315</v>
       </c>
       <c r="F91">
-        <v>-5.297365784677997</v>
+        <v>-5.431004641036837</v>
       </c>
       <c r="G91">
-        <v>-4.152087366022257</v>
+        <v>-2.925281952806837</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.679943699893917</v>
       </c>
       <c r="E92">
-        <v>-25.35910782716301</v>
+        <v>-26.05515239603798</v>
       </c>
       <c r="F92">
-        <v>-5.854588655723558</v>
+        <v>-5.59581496276302</v>
       </c>
       <c r="G92">
-        <v>-4.917697369616269</v>
+        <v>-2.701588390718282</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.826063398236672</v>
       </c>
       <c r="E93">
-        <v>-27.64094700946601</v>
+        <v>-26.79510504889132</v>
       </c>
       <c r="F93">
-        <v>-6.025369021321718</v>
+        <v>-5.865647360550931</v>
       </c>
       <c r="G93">
-        <v>-5.115853383414884</v>
+        <v>-3.225435874670398</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.035862294939799</v>
       </c>
       <c r="E94">
-        <v>-30.16621884052533</v>
+        <v>-30.2355112855537</v>
       </c>
       <c r="F94">
-        <v>-5.607133774954873</v>
+        <v>-6.108957090836008</v>
       </c>
       <c r="G94">
-        <v>-5.675921546112166</v>
+        <v>-3.497337600901819</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.310717300875886</v>
       </c>
       <c r="E95">
-        <v>-31.097064786698</v>
+        <v>-32.32163208548218</v>
       </c>
       <c r="F95">
-        <v>-5.837946754601316</v>
+        <v>-6.466489573925705</v>
       </c>
       <c r="G95">
-        <v>-5.707073779636708</v>
+        <v>-3.788857619998961</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.640242800787446</v>
       </c>
       <c r="E96">
-        <v>-33.80410730018821</v>
+        <v>-33.68374725377534</v>
       </c>
       <c r="F96">
-        <v>-6.260972449658551</v>
+        <v>-6.444772265726511</v>
       </c>
       <c r="G96">
-        <v>-5.082291072737753</v>
+        <v>-4.933240380923147</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.998731692521463</v>
       </c>
       <c r="E97">
-        <v>-36.44230795181381</v>
+        <v>-36.49983768560725</v>
       </c>
       <c r="F97">
-        <v>-6.348060371449669</v>
+        <v>-6.625198141362868</v>
       </c>
       <c r="G97">
-        <v>-6.82417433477176</v>
+        <v>-4.779799905723467</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.368418552605175</v>
       </c>
       <c r="E98">
-        <v>-39.38433977427304</v>
+        <v>-39.13643299319713</v>
       </c>
       <c r="F98">
-        <v>-6.207282644813503</v>
+        <v>-6.827448184593381</v>
       </c>
       <c r="G98">
-        <v>-7.001089888390412</v>
+        <v>-5.201599823427547</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.717471772801618</v>
       </c>
       <c r="E99">
-        <v>-41.01642444900747</v>
+        <v>-42.09337255208961</v>
       </c>
       <c r="F99">
-        <v>-6.996863400711728</v>
+        <v>-6.913686201429226</v>
       </c>
       <c r="G99">
-        <v>-6.909238802403332</v>
+        <v>-6.217324853059037</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.031037699367864</v>
       </c>
       <c r="E100">
-        <v>-44.21659061108893</v>
+        <v>-44.71967237402306</v>
       </c>
       <c r="F100">
-        <v>-7.012432980231046</v>
+        <v>-7.018535148703768</v>
       </c>
       <c r="G100">
-        <v>-7.649225183523385</v>
+        <v>-5.731220898800152</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.272626310780806</v>
       </c>
       <c r="E101">
-        <v>-46.32181477861878</v>
+        <v>-47.13070212705387</v>
       </c>
       <c r="F101">
-        <v>-7.18434489570143</v>
+        <v>-6.859683273705921</v>
       </c>
       <c r="G101">
-        <v>-8.305981139240622</v>
+        <v>-6.49980377228843</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.463847806239636</v>
       </c>
       <c r="E102">
-        <v>-50.01820885822375</v>
+        <v>-49.00502393340661</v>
       </c>
       <c r="F102">
-        <v>-6.622463700566227</v>
+        <v>-7.087307038851586</v>
       </c>
       <c r="G102">
-        <v>-9.108334887775005</v>
+        <v>-7.353785478507747</v>
       </c>
     </row>
   </sheetData>
